--- a/체험단_문자발송_리스트.xlsx
+++ b/체험단_문자발송_리스트.xlsx
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>010-7490-3175(X)</t>
+          <t>010-7490-3175</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>010-7360-5998(X)</t>
+          <t>010-7360-5998</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>010-2187-1826(X)</t>
+          <t>010-2187-1826</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>010-2830-5915(X)</t>
+          <t>010-2830-5915</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>010-6699-8867(X)</t>
+          <t>010-6699-8867</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>010-2189-6146(X)</t>
+          <t>010-2189-6146</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>010-8039-0914(X)</t>
+          <t>010-8039-0914</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>010-8053-0716(X)</t>
+          <t>010-8053-0716</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>010-4044-9770(X)</t>
+          <t>010-4044-9770</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>010-5722-2606(X)</t>
+          <t>010-5722-2606</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>010-2475-5632(X)</t>
+          <t>010-2475-5632</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>010-3953-3976(X)</t>
+          <t>010-3953-3976</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>010-4985-0227(X)</t>
+          <t>010-4985-0227</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>010-4080-0816(X)</t>
+          <t>010-4080-0816</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>010-6829-1853(X)</t>
+          <t>010-6829-1853</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>010-2459-5439(X)</t>
+          <t>010-2459-5439</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>010-8832-8321(X)</t>
+          <t>010-8832-8321</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>010-4285-4808(X)</t>
+          <t>010-4285-4808</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>010-2184-2406(X)</t>
+          <t>010-2184-2406</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>010-5267-9954(X)</t>
+          <t>010-5267-9954</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>010-2190-6977(X)</t>
+          <t>010-2190-6977</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>010-7479-7379(X)</t>
+          <t>010-7479-7379</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>010-9748-6355(X)</t>
+          <t>010-9748-6355</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>010-6470-3314(X)</t>
+          <t>010-6470-3314</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>010-4259-7925(X)</t>
+          <t>010-4259-7925</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>010-7297-2589(X)</t>
+          <t>010-7297-2589</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>010-5756-2674(X)</t>
+          <t>010-5756-2674</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>010-8363-6572(X)</t>
+          <t>010-8363-6572</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>010-4345-9923(X)</t>
+          <t>010-4345-9923</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>010-2007-3348(X)</t>
+          <t>010-2007-3348</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>010-2832-8564(X)</t>
+          <t>010-2832-8564</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>010-6829-3373(X)</t>
+          <t>010-6829-3373</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>010-2267-4804(X)</t>
+          <t>010-2267-4804</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>010-5450-0322(X)</t>
+          <t>010-5450-0322</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>010-5967-6921(X)</t>
+          <t>010-5967-6921</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>010-8249-5345(X)</t>
+          <t>010-8249-5345</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>010-4291-7733(X)</t>
+          <t>010-4291-7733</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>010-7307-2721(X)</t>
+          <t>010-7307-2721</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>010-6862-0278(X)</t>
+          <t>010-6862-0278</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>010-5865-4517(X)</t>
+          <t>010-5865-4517</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>010-2895-5280(X)</t>
+          <t>010-2895-5280</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>010-8062-6302(X)</t>
+          <t>010-8062-6302</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>010-3929-1572(X)</t>
+          <t>010-3929-1572</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>010-9778-4323(X)</t>
+          <t>010-9778-4323</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>010-5023-3663(X)</t>
+          <t>010-5023-3663</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>010-6842-4425(X)</t>
+          <t>010-6842-4425</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>010-6624-9810(X)</t>
+          <t>010-6624-9810</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>010-5562-2801(X)</t>
+          <t>010-5562-2801</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>010-8022-1556(X)</t>
+          <t>010-8022-1556</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>010-5400-5103(X)</t>
+          <t>010-5400-5103</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>010-8226-4156(X)</t>
+          <t>010-8226-4156</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>010-6827-1963(X)</t>
+          <t>010-6827-1963</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>010-7623-4157(X)</t>
+          <t>010-7623-4157</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>010-4452-3616(X)</t>
+          <t>010-4452-3616</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>010-6740-2311(X)</t>
+          <t>010-6740-2311</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>010-9887-2617(X)</t>
+          <t>010-9887-2617</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>010-4830-7629(X)</t>
+          <t>010-4830-7629</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>010-9726-1156(X)</t>
+          <t>010-9726-1156</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>010-9642-7704(X)</t>
+          <t>010-9642-7704</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>010-7444-6546(X)</t>
+          <t>010-7444-6546</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>010-8925-5060(X)</t>
+          <t>010-8925-5060</t>
         </is>
       </c>
     </row>
@@ -6256,31 +6256,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>010-8306-1277(X)</t>
+          <t>010-8306-1277</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>010-8991-7784(X)</t>
+          <t>010-8991-7784</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>010-8991-7784(X)</t>
+          <t>010-8991-7784</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>010-239-6219(X)</t>
+          <t>010-239-6219</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>010-239-6219(X)</t>
+          <t>010-239-6219</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>010-2942-7290(X)</t>
+          <t>010-2942-7290</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>010-6895-8965(X)</t>
+          <t>010-6895-8965</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>010-9538-3220(X)</t>
+          <t>010-9538-3220</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>010-2297-7675(X)</t>
+          <t>010-2297-7675</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>010-2150-0069(X)</t>
+          <t>010-2150-0069</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>010-6715-5322(X)</t>
+          <t>010-6715-5322</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>010-8096-5458(X)</t>
+          <t>010-8096-5458</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>010-6554-4261(X)</t>
+          <t>010-6554-4261</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>010-6827-9560(X)</t>
+          <t>010-6827-9560</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>010-8210-8885(X)</t>
+          <t>010-8210-8885</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>010-4413-0372(X)</t>
+          <t>010-4413-0372</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>010-5727-7518(X)</t>
+          <t>010-5727-7518</t>
         </is>
       </c>
     </row>

--- a/체험단_문자발송_리스트.xlsx
+++ b/체험단_문자발송_리스트.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,5662 +911,4690 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>이세인</t>
+          <t>운텐 마이코</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>010-2291-3925</t>
+          <t>010-3225-2646</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>운텐 마이코</t>
+          <t>김사미</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>010-3225-2646</t>
+          <t>010-3101-5913</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>김사미</t>
+          <t>데구치 모에카</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>010-3101-5913</t>
+          <t>010-6276-1884</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>데구치 모에카</t>
+          <t>오오타 메이</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>010-6276-1884</t>
+          <t>010-5059-2531</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>오오타 메이</t>
+          <t>코스기 아스카</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>010-5059-2531</t>
+          <t>010-8201-2261</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>코스기 아스카</t>
+          <t>키시야 하루나</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>010-8201-2261</t>
+          <t>010-8097-0252</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>키시야 하루나</t>
+          <t>코바야시 사나에</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>010-8097-0252</t>
+          <t>010-3576-5107</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>코바야시 사나에</t>
+          <t>우에다 아키</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>010-3576-5107</t>
+          <t>010-6634-8311</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>우에다 아키</t>
+          <t>강레나</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>010-6634-8311</t>
+          <t>010-3328-1413</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>강레나</t>
+          <t>코마츠 미사토</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>010-3328-1413</t>
+          <t>010-3028-6830</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>코마츠 미사토</t>
+          <t>방유의</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>010-3028-6830</t>
+          <t>010-6784-0406</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>방유의</t>
+          <t>아즈마 요시에</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>010-6784-0406</t>
+          <t>010-4079-6020</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>아즈마 요시에</t>
+          <t>야마구치 히나코</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>010-4079-6020</t>
+          <t>010-9574-4707</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>야마구치 히나코</t>
+          <t>키쿠치 미호</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>010-9574-4707</t>
+          <t>010-3057-1905</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>키쿠치 미호</t>
+          <t>야시로 에리</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>010-3057-1905</t>
+          <t>010-9577-2847</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>야시로 에리</t>
+          <t>기무라 미카</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>010-9577-2847</t>
+          <t>010-5116-0832</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>기무라 미카</t>
+          <t>아세치 키미</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>010-5116-0832</t>
+          <t>010-5481-0821</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>아세치 키미</t>
+          <t>다치모리 기요에</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>010-5481-0821</t>
+          <t>010-2419-3212</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>다치모리 기요에</t>
+          <t>오와다 기요미</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>010-2419-3212</t>
+          <t>010-7118-6582</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>오와다 기요미</t>
+          <t>후쿠이 소노미</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>010-7118-6582</t>
+          <t>010-4568-7425</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>후쿠이 소노미</t>
+          <t>마사코</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>010-4568-7425</t>
+          <t>010-8274-7909</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>마사코</t>
+          <t>이유리</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>010-8274-7909</t>
+          <t>010-4415-1019</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>이유리</t>
+          <t>다카기 유우키</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>010-4415-1019</t>
+          <t>010-3409-5020</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>다카기 유우키</t>
+          <t>사도 히메카</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>010-3409-5020</t>
+          <t>010-3103-1998</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>사도 히메카</t>
+          <t>사까베 히토미</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>010-3103-1998</t>
+          <t>010-6505-0216</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>사까베 히토미</t>
+          <t>후쿠시마 유카코</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>010-6505-0216</t>
+          <t>010-4314-7371</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>후쿠시마 유카코</t>
+          <t>사카구치 츠구미</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>010-4314-7371</t>
+          <t>010-3053-9902</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>사카구치 츠구미</t>
+          <t>우라 니지호</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>010-3053-9902</t>
+          <t>010-7233-0059</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>우라 니지호</t>
+          <t>나카 유키</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>010-7233-0059</t>
+          <t>010-7584-0917</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>나카 유키</t>
+          <t>후루쇼 히나</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>010-7584-0917</t>
+          <t>010-2645-6877</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>후루쇼 히나</t>
+          <t>카타다 사치</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>010-2645-6877</t>
+          <t>010-5731-2137</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>카타다 사치</t>
+          <t>요네마수 라무</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>010-5731-2137</t>
+          <t>010-8319-8626</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>요네마수 라무</t>
+          <t>리키</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>010-8319-8626</t>
+          <t>010-3078-5366</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>리키</t>
+          <t>김정현</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>010-3078-5366</t>
+          <t>010-6886-3354</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>김정현</t>
+          <t>강서가</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>010-6886-3354</t>
+          <t>010-9687-2090</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강서가</t>
+          <t>장효은</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>010-9687-2090</t>
+          <t>010-3086-7005</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>장효은</t>
+          <t>요시다 모모카</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>010-3086-7005</t>
+          <t>010-4485-0314</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>요시다 모모카</t>
+          <t>하기오 메이</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>010-4485-0314</t>
+          <t>010-2969-5043</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>하기오 메이</t>
+          <t>스가야 유미</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>010-2969-5043</t>
+          <t>010-2975-1436</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>스가야 유미</t>
+          <t>토키타 쿠미코</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>010-2975-1436</t>
+          <t>010-2957-9904</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>토키타 쿠미코</t>
+          <t>CHOI KARIN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>010-2957-9904</t>
+          <t>010-6875-7280</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHOI KARIN</t>
+          <t>마츠모토 토모코</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>010-6875-7280</t>
+          <t>010-4466-6537</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>마츠모토 토모코</t>
+          <t>하마다 유이</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>010-4466-6537</t>
+          <t>010-5129-5533</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>하마다 유이</t>
+          <t>크리스 하루나</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>010-5129-5533</t>
+          <t>010-2475-6266</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>이케다 아마네</t>
+          <t>미쿠치 치아키</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>080-3015-1299</t>
+          <t>010-9432-0339</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>크리스 하루나</t>
+          <t>무라야마 유이노</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>010-2475-6266</t>
+          <t>010-3083-1096</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>미쿠치 치아키</t>
+          <t>이 마리야</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>010-9432-0339</t>
+          <t>010-5691-0322</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>무라야마 유이노</t>
+          <t>무라카미 미츠요</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>010-3083-1096</t>
+          <t>010-2048-4660</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>이 마리야</t>
+          <t>이와모토 유카</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>010-5691-0322</t>
+          <t>010-3192-5915</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>무라카미 미츠요</t>
+          <t>하루카</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>010-2048-4660</t>
+          <t>010-2808-4508</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>이와모토 유카</t>
+          <t>요시다 모카</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>010-3192-5915</t>
+          <t>010-2610-2034</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>하루카</t>
+          <t>혼다 시오리</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>010-2808-4508</t>
+          <t>010-4603-4424</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>요시다 모카</t>
+          <t>토쿠나가 케이코</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>010-2610-2034</t>
+          <t>010-7610-0403</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>혼다 시오리</t>
+          <t>이토 사쿠라</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>010-4603-4424</t>
+          <t>010-7675-8197</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>토쿠나가 케이코</t>
+          <t>오카다 아야</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>010-7610-0403</t>
+          <t>010-5187-2157</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>이토 사쿠라</t>
+          <t>히토미</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>010-7675-8197</t>
+          <t>010-2181-7946</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>오카다 아야</t>
+          <t>허유라</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>010-5187-2157</t>
+          <t>010-7298-0416</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>히토미</t>
+          <t>몬구치 토모</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>010-2181-7946</t>
+          <t>010-7772-3352</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>허유라</t>
+          <t>고쿠보 히사에</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>010-7298-0416</t>
+          <t>010-2369-0225</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>몬구치 토모</t>
+          <t>이토 노아</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>010-7772-3352</t>
+          <t>010-8156-8189</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>고쿠보 히사에</t>
+          <t>아이자와 사오리</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>010-2369-0225</t>
+          <t>010-5311-3254</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>나카무라 리에</t>
+          <t>츠치야 호노카</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>080-5358-3059</t>
+          <t>010-4496-9822</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>이토 노아</t>
+          <t>야스다 토모에</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>010-8156-8189</t>
+          <t>010-3811-5700</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>아이자와 사오리</t>
+          <t>옹효석</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>010-5311-3254</t>
+          <t>010-4794-7867</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>츠치야 호노카</t>
+          <t>오하타 에미이</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>010-4496-9822</t>
+          <t>010-3907-6598</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>야스다 토모에</t>
+          <t>니시바야시 아미</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>010-3811-5700</t>
+          <t>010-4011-9403</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>옹효석</t>
+          <t>이마에다 나미</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>010-4794-7867</t>
+          <t>010-4219-0422</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>오하타 에미이</t>
+          <t>미사키</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>010-3907-6598</t>
+          <t>010-2182-4408</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>니시바야시 아미</t>
+          <t>마츠모토 미호</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>010-4011-9403</t>
+          <t>010-8255-4222</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>이마에다 나미</t>
+          <t>노노구치 카오리</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>010-4219-0422</t>
+          <t>010-3074-5606</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>미사키</t>
+          <t>노무라 사키</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>010-2182-4408</t>
+          <t>010-4274-0024</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>야자와 나나미</t>
+          <t>나카무라 아야</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>010-8424-0481</t>
+          <t>010-9948-4143</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>마츠모토 미호</t>
+          <t>후지사와 미즈에</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>010-8255-4222</t>
+          <t>010-3954-6112</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>노노구치 카오리</t>
+          <t>아베 유메노</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>010-3074-5606</t>
+          <t>010-7624-3906</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>노무라 사키</t>
+          <t>후지모토 코코</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>010-4274-0024</t>
+          <t>010-6508-0227</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>나카무라 아야</t>
+          <t>와타나베 미사키</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>010-9948-4143</t>
+          <t>010-4325-9400</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>후지사와 미즈에</t>
+          <t>와키모토 사키</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>010-3954-6112</t>
+          <t>010-9704-5929</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>아베 유메노</t>
+          <t>히라사와 유이</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>010-7624-3906</t>
+          <t>010-9659-5325</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>후지모토 코코</t>
+          <t>쿠보타 츠쿠시</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>010-6508-0227</t>
+          <t>010-3222-5684</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>와타나베 미사키</t>
+          <t>이노우에 카나하</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>010-4325-9400</t>
+          <t>010-5733-0491</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>와키모토 사키</t>
+          <t>사카베 유카</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>010-9704-5929</t>
+          <t>010-7397-7597</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>히라사와 유이</t>
+          <t>야마시로 사키나</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>010-9659-5325</t>
+          <t>010-4432-0965</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>쿠보타 츠쿠시</t>
+          <t>나가세 미유키</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>010-3222-5684</t>
+          <t>010-7204-4664</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>이노우에 카나하</t>
+          <t>나카가와 소노카</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>010-5733-0491</t>
+          <t>010-9490-6051</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>사카베 유카</t>
+          <t>와타바야시 유이나</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>010-7397-7597</t>
+          <t>010-7781-1719</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>야마시로 사키나</t>
+          <t>마사미</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>010-4432-0965</t>
+          <t>010-3085-1139</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>나가세 미유키</t>
+          <t>마츠야 아야</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>010-7204-4664</t>
+          <t>010-6703-6798</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>나카가와 소노카</t>
+          <t>윤하루</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>010-9490-6051</t>
+          <t>010-4553-1834</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>와타바야시 유이나</t>
+          <t>야마자키 유호</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>010-7781-1719</t>
+          <t>010-6422-3453</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>마사미</t>
+          <t>하루카</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>010-3085-1139</t>
+          <t>010-2563-0064</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>마츠야 아야</t>
+          <t>야마네 료코</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>010-6703-6798</t>
+          <t>010-8237-4421</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>윤하루</t>
+          <t>권리사</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>010-4553-1834</t>
+          <t>010-3904-0729</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>야마자키 유호</t>
+          <t>카타다 유우</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>010-6422-3453</t>
+          <t>010-5736-2137</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>하루카</t>
+          <t>이정희</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>010-2563-0064</t>
+          <t>010-9625-2465</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>야마네 료코</t>
+          <t>야마네 마이코</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>010-8237-4421</t>
+          <t>010-4230-1096</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>권리사</t>
+          <t>시바타 마야</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>010-3904-0729</t>
+          <t>010-4223-0212</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>카타다 유우</t>
+          <t>아카사카 유우코</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>010-5736-2137</t>
+          <t>010-5718-7990</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>이정희</t>
+          <t>요시노 마이</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>010-9625-2465</t>
+          <t>010-2889-3290</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>야마네 마이코</t>
+          <t>유미</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>010-4230-1096</t>
+          <t>010-5531-6152</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>시바타 마야</t>
+          <t>김민지</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>010-4223-0212</t>
+          <t>010-3152-7726</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>아카사카 유우코</t>
+          <t>히사노 히토미</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>010-5718-7990</t>
+          <t>010-6638-1947</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>요시노 마이</t>
+          <t>야마타니 마이</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>010-2889-3290</t>
+          <t>010-4328-4282</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>유미</t>
+          <t>오오모모 아야네</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>010-5531-6152</t>
+          <t>010-8215-2107</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>김민지</t>
+          <t>김마미</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>010-3152-7726</t>
+          <t>010-7559-7355</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>히사노 히토미</t>
+          <t>키도 레나</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>010-6638-1947</t>
+          <t>010-3926-4490</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>야마타니 마이</t>
+          <t>세기자와 미카</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>010-4328-4282</t>
+          <t>010-5806-0113</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>오오모모 아야네</t>
+          <t>사사키 키요미</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>010-8215-2107</t>
+          <t>010-4386-6126</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>김마미</t>
+          <t>미타니 아카리</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>010-7559-7355</t>
+          <t>010-3394-5500</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>키도 레나</t>
+          <t>에이코</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>010-3926-4490</t>
+          <t>010-9480-0916</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>세기자와 미카</t>
+          <t>타구치 유마</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>010-5806-0113</t>
+          <t>010-7539-9784</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>사사키 키요미</t>
+          <t>코마츠 마도카</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>010-4386-6126</t>
+          <t>010-4298-7976</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>미타니 아카리</t>
+          <t>오바라 카나코</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>010-3394-5500</t>
+          <t>010-9926-8341</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>에이코</t>
+          <t>김가나</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>010-9480-0916</t>
+          <t>010-5400-5413</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>타구치 유마</t>
+          <t>타나카 사쿠라</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>010-7539-9784</t>
+          <t>010-9730-7719</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>코마츠 마도카</t>
+          <t>유키노</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>010-4298-7976</t>
+          <t>010-4358-6831</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>오바라 카나코</t>
+          <t>후루세 히나</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>010-9926-8341</t>
+          <t>010-7659-9834</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>김가나</t>
+          <t>이시다 아야코</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>010-5400-5413</t>
+          <t>010-8178-2170</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>타나카 사쿠라</t>
+          <t>모에노</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>010-9730-7719</t>
+          <t>010-6551-1039</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>유키노</t>
+          <t>미츠시로 유</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>010-4358-6831</t>
+          <t>010-8831-1789</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>후루세 히나</t>
+          <t>마루타 하즈키</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>010-7659-9834</t>
+          <t>010-2993-6505</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>이시다 아야코</t>
+          <t>이치조 마유</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>010-8178-2170</t>
+          <t>010-2847-8045</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>모에노</t>
+          <t>후쿠모토 마나</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>010-6551-1039</t>
+          <t>010-8267-3377</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>미츠시로 유</t>
+          <t>네지메 사키</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>010-8831-1789</t>
+          <t>010-2692-3283</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>마루타 하즈키</t>
+          <t>오구라 유이</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>010-2993-6505</t>
+          <t>010-3976-8739</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>이치조 마유</t>
+          <t>나보미</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>010-2847-8045</t>
+          <t>010-7385-2274</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>후쿠모토 마나</t>
+          <t>하야시 리나</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>010-8267-3377</t>
+          <t>010-2250-7926</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>네지메 사키</t>
+          <t>히로타 츠카사</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>010-2692-3283</t>
+          <t>010-5945-4006</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>오구라 유이</t>
+          <t>이사비</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>010-3976-8739</t>
+          <t>010-9232-9470</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>나보미</t>
+          <t>시오야 이쿠미</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>010-7385-2274</t>
+          <t>010-3976-2750</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>하야시 리나</t>
+          <t>노다 카준</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>010-2250-7926</t>
+          <t>010-7797-2093</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>히로타 츠카사</t>
+          <t>오카와 미사토</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>010-5945-4006</t>
+          <t>010-5168-5549</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>이사비</t>
+          <t>오바 마리</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>010-9232-9470</t>
+          <t>010-7390-9026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>시오야 이쿠미</t>
+          <t>야마나카 유키</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>010-3976-2750</t>
+          <t>010-6461-6123</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>노다 카준</t>
+          <t>스에요시 카나코</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>010-7797-2093</t>
+          <t>010-8566-2256</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>오카와 미사토</t>
+          <t>이와이 치나미</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>010-5168-5549</t>
+          <t>010-3407-4860</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>오바 마리</t>
+          <t>야마모토 아리사</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>010-7390-9026</t>
+          <t>010-5362-5317</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>야마나카 유키</t>
+          <t>마츠야마 나츠키</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>010-6461-6123</t>
+          <t>010-9895-6301</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>스에요시 카나코</t>
+          <t>도치모토 미호</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>010-8566-2256</t>
+          <t>010-8070-7486</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>이와이 치나미</t>
+          <t>아마리 미호</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>010-3407-4860</t>
+          <t>010-3400-7291</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>야마모토 아리사</t>
+          <t>오노 마이</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>010-5362-5317</t>
+          <t>010-8274-3060</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>마츠야마 나츠키</t>
+          <t>유노끼 토모에</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>010-9895-6301</t>
+          <t>010-4762-6120</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>도치모토 미호</t>
+          <t>최리혜</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>010-8070-7486</t>
+          <t>010-3086-0786</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>아마리 미호</t>
+          <t>후지노 하루애</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>010-3400-7291</t>
+          <t>010-5729-8325</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>오노 마이</t>
+          <t>이미란</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>010-8274-3060</t>
+          <t>010-2712-4921</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>유노끼 토모에</t>
+          <t>아사노 와카나</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>010-4762-6120</t>
+          <t>010-2671-3187</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>최리혜</t>
+          <t>박고은</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>010-3086-0786</t>
+          <t>010-6485-9273</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>후지노 하루애</t>
+          <t>다나카 레이나</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>010-5729-8325</t>
+          <t>010-5969-4150</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>이미란</t>
+          <t>박 수잠마리아</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>010-2712-4921</t>
+          <t>010-3061-7458</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>아사노 와카나</t>
+          <t>쿠로카와 마사키</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>010-2671-3187</t>
+          <t>010-8199-0955</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>박고은</t>
+          <t>오카모토 미사</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>010-6485-9273</t>
+          <t>010-6677-6923</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>다나카 레이나</t>
+          <t>이시카와 에리나</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>010-5969-4150</t>
+          <t>010-4892-9826</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>박 수잠마리아</t>
+          <t>츠부라야 아사미</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>010-3061-7458</t>
+          <t>010-3367-5606</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>쿠로카와 마사키</t>
+          <t>나카지마 미키</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>010-8199-0955</t>
+          <t>010-8362-7992</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>오카모토 미사</t>
+          <t>야마모토 유카</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>010-6677-6923</t>
+          <t>010-7422-0522</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>이시카와 에리나</t>
+          <t>김영이</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>010-4892-9826</t>
+          <t>010-8060-0427</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>츠부라야 아사미</t>
+          <t>마루모 시즈카</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>010-3367-5606</t>
+          <t>010-3982-5911</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>나카지마 미키</t>
+          <t>안미선</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>010-8362-7992</t>
+          <t>010-6599-6856</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>야마모토 유카</t>
+          <t>쿠마타키 아오이</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>010-7422-0522</t>
+          <t>010-8064-0051</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>김영이</t>
+          <t>아야메</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>010-8060-0427</t>
+          <t>010-6489-4669</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>마루모 시즈카</t>
+          <t>이에후지 미레이</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>010-3982-5911</t>
+          <t>010-2535-8099</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>안미선</t>
+          <t>아라마키 모에카</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>010-6599-6856</t>
+          <t>010-8981-0401</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>쿠마타키 아오이</t>
+          <t>오쿠무라 미코토</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>010-8064-0051</t>
+          <t>010-5960-3610</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>아야메</t>
+          <t>오쿠무라 시즈카</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>010-6489-4669</t>
+          <t>010-9624-8877</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>이에후지 미레이</t>
+          <t>오노 쿠레하</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>010-2535-8099</t>
+          <t>010-5573-9783</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>아라마키 모에카</t>
+          <t>기타다 모모꼬</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>010-8981-0401</t>
+          <t>010-4387-1172</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>오쿠무라 미코토</t>
+          <t>이마키</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>010-5960-3610</t>
+          <t>010-6441-9092</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>오쿠무라 시즈카</t>
+          <t>사토 유키나</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>010-9624-8877</t>
+          <t>010-2403-8810</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>오노 쿠레하</t>
+          <t>나카무라 유나</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>010-5573-9783</t>
+          <t>010-9867-3156</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>기타다 모모꼬</t>
+          <t>코노미</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>010-4387-1172</t>
+          <t>010-6576-8225</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>이마키</t>
+          <t>김인미</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>010-6441-9092</t>
+          <t>010-7539-1531</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>사토 유키나</t>
+          <t>아라카와 나나</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>010-2403-8810</t>
+          <t>010-7366-1791</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>나카무라 유나</t>
+          <t>나카가와 유카</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>010-9867-3156</t>
+          <t>010-7515-2981</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>코노미</t>
+          <t>정 타마미</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>010-6576-8225</t>
+          <t>010-5892-6096</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>김인미</t>
+          <t>김영주</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>010-7539-1531</t>
+          <t>010-2100-9105</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>아라카와 나나</t>
+          <t>시오자키 에리</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>010-7366-1791</t>
+          <t>010-5840-2645</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>나카가와 유카</t>
+          <t>이소가이 사유리</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>010-7515-2981</t>
+          <t>010-4295-2325</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>정 타마미</t>
+          <t>정 미즈키</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>010-5892-6096</t>
+          <t>010-8380-3853</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>김영주</t>
+          <t>하야시 나나카</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>010-2100-9105</t>
+          <t>010-4219-7127</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>시오자키 에리</t>
+          <t>히사나가 유키노</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>010-5840-2645</t>
+          <t>010-5944-7491</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>이소가이 사유리</t>
+          <t>이유화</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>010-4295-2325</t>
+          <t>010-2826-0552</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>정 미즈키</t>
+          <t>강회미</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>010-8380-3853</t>
+          <t>010-5859-3005</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>하야시 나나카</t>
+          <t>오쿠다 미사키</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>010-4219-7127</t>
+          <t>010-8582-7990</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>히사나가 유키노</t>
+          <t>남윤호</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>010-5944-7491</t>
+          <t>010-2062-3342</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>이유화</t>
+          <t>나카무라 나츠코</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>010-2826-0552</t>
+          <t>010-3453-0863</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>강회미</t>
+          <t>스즈키 유우카</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>010-5859-3005</t>
+          <t>010-9938-4613</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>오쿠다 미사키</t>
+          <t>사토 요시코</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>010-8582-7990</t>
+          <t>010-6698-1904</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>남윤호</t>
+          <t>사노 미사키</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>010-2062-3342</t>
+          <t>010-8119-9833</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>나카무라 나츠코</t>
+          <t>오자와 사키에</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>010-3453-0863</t>
+          <t>010-4414-0235</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>스즈키 유우카</t>
+          <t>소리 미유키</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>010-9938-4613</t>
+          <t>010-2439-4189</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>사토 요시코</t>
+          <t>천미키</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>010-6698-1904</t>
+          <t>010-8499-7800</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>사노 미사키</t>
+          <t>유키 레이라</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>010-8119-9833</t>
+          <t>010-4252-8166</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>오자와 사키에</t>
+          <t>샤쿠토 모에</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>010-4414-0235</t>
+          <t>010-9771-5963</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>소리 미유키</t>
+          <t>나츠미</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>010-2439-4189</t>
+          <t>010-7231-9701</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>천미키</t>
+          <t>다자와 가나에</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>010-8499-7800</t>
+          <t>010-8459-1045</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>유키 레이라</t>
+          <t>시미즈 아야코</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>010-4252-8166</t>
+          <t>010-2478-1184</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>샤쿠토 모에</t>
+          <t>요네야마 쿄우코</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>010-9771-5963</t>
+          <t>010-3210-7612</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>나츠미</t>
+          <t>노도희</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>010-7231-9701</t>
+          <t>010-5637-8206</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>다자와 가나에</t>
+          <t>키노시타 아사카</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>010-8459-1045</t>
+          <t>010-4950-6177</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>시미즈 아야코</t>
+          <t>하토리 에리코</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>010-2478-1184</t>
+          <t>010-2960-2208</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>요네야마 쿄우코</t>
+          <t>히라마 하나</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>010-3210-7612</t>
+          <t>010-6689-3437</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>노도희</t>
+          <t>이사나</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>010-5637-8206</t>
+          <t>010-2581-2407</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>키노시타 아사카</t>
+          <t>탄지 미즈키</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>010-4950-6177</t>
+          <t>010-4487-0751</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>하토리 에리코</t>
+          <t>타카하시 아야카</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>010-2960-2208</t>
+          <t>010-7415-7650</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>히라마 하나</t>
+          <t>이토 모모코</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>010-6689-3437</t>
+          <t>010-2637-3407</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>이사나</t>
+          <t>다나카 에리카</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>010-2581-2407</t>
+          <t>010-3480-2260</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>탄지 미즈키</t>
+          <t>리사</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>010-4487-0751</t>
+          <t>010-4491-9596</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>타카하시 아야카</t>
+          <t>후지야마 치히로</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>010-7415-7650</t>
+          <t>010-3499-6027</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>이토 모모코</t>
+          <t>호리에 나츠키</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>010-2637-3407</t>
+          <t>010-8175-7950</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>다나카 에리카</t>
+          <t>우다 아이리</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>010-3480-2260</t>
+          <t>010-4280-8935</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>리사</t>
+          <t>오카다 호노카</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>010-4491-9596</t>
+          <t>010-5429-2569</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>후지야마 치히로</t>
+          <t>시마다 치나미</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>010-3499-6027</t>
+          <t>010-2115-8653</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>호리에 나츠키</t>
+          <t>호나미</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>010-8175-7950</t>
+          <t>010-2742-3478</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>우다 아이리</t>
+          <t>미요코</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>010-4280-8935</t>
+          <t>010-2417-1316</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>오카다 호노카</t>
+          <t>에토 아야나</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>010-5429-2569</t>
+          <t>010-2684-4799</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>시마다 치나미</t>
+          <t>오키무라 마리</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>010-2115-8653</t>
+          <t>010-7408-0925</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>호나미</t>
+          <t>사토 아이미</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>010-2742-3478</t>
+          <t>010-2676-7614</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>미요코</t>
+          <t>사오리</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>010-2417-1316</t>
+          <t>010-4919-6090</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>에토 아야나</t>
+          <t>후쿠모토 아이코</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>010-2684-4799</t>
+          <t>010-8257-7649</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>오키무라 마리</t>
+          <t>황지혜</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>010-7408-0925</t>
+          <t>010-5045-3287</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>사토 아이미</t>
+          <t>사토 리카</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>010-2676-7614</t>
+          <t>010-5049-5988</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>사오리</t>
+          <t>오쿠이즈미 하츠네</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>010-4919-6090</t>
+          <t>010-8376-7932</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>후쿠모토 아이코</t>
+          <t>하야시 미사토</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>010-8257-7649</t>
+          <t>010-2157-2342</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>황지혜</t>
+          <t>시미즈</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>010-5045-3287</t>
+          <t>010-6262-8670</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>사토 리카</t>
+          <t>호리구치 히나타</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>010-5049-5988</t>
+          <t>010-8061-2166</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>오쿠이즈미 하츠네</t>
+          <t>아사이 유리</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>010-8376-7932</t>
+          <t>010-5189-5430</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>하야시 미사토</t>
+          <t>모리타 유카</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>010-2157-2342</t>
+          <t>010-5524-8104</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>시미즈</t>
+          <t>야마모토 마린</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>010-6262-8670</t>
+          <t>010-8022-8625</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>호리구치 히나타</t>
+          <t>에 아사미</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>010-8061-2166</t>
+          <t>010-7726-7695</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>아사이 유리</t>
+          <t>마츠다이라 카나코</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>010-5189-5430</t>
+          <t>010-3951-5250</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>모리타 유카</t>
+          <t>쿠보타 미호</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>010-5524-8104</t>
+          <t>010-2982-8214</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>야마모토 마린</t>
+          <t>우에나까 치하루</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>010-8022-8625</t>
+          <t>010-9540-8586</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>에 아사미</t>
+          <t>와타나베 쿠미코</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>010-7726-7695</t>
+          <t>010-5415-9353</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>마츠다이라 카나코</t>
+          <t>하루야마 미쿠</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>010-3951-5250</t>
+          <t>010-8278-9362</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>쿠보타 미호</t>
+          <t>시바타 마나</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>010-2982-8214</t>
+          <t>010-6680-5126</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>우에나까 치하루</t>
+          <t>나츠미</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>010-9540-8586</t>
+          <t>010-9552-7718</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>와타나베 쿠미코</t>
+          <t>마나리</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>010-5415-9353</t>
+          <t>010-8199-6658</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>하루야마 미쿠</t>
+          <t>가네무라 진</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>010-8278-9362</t>
+          <t>010-5890-9635</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>시바타 마나</t>
+          <t>타카자와 미스즈</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>010-6680-5126</t>
+          <t>010-5701-5762</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>나츠미</t>
+          <t>키타무라 유우</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>010-9552-7718</t>
+          <t>010-8308-5192</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>마나리</t>
+          <t>사메지마 시온</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>010-8199-6658</t>
+          <t>010-7232-8563</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>가네무라 진</t>
+          <t>야스하라 미즈키</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>010-5890-9635</t>
+          <t>010-3056-3201</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>타카자와 미스즈</t>
+          <t>하토리 세나</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>010-5701-5762</t>
+          <t>010-9531-7235</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>키타무라 유우</t>
+          <t>니시다 아카리</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>010-8308-5192</t>
+          <t>010-8377-8516</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>사메지마 시온</t>
+          <t>하토리 유키</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>010-7232-8563</t>
+          <t>010-7239-8682</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>야스하라 미즈키</t>
+          <t>고노 나오</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>010-3056-3201</t>
+          <t>010-2438-2448</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>하토리 세나</t>
+          <t>황수지</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>010-9531-7235</t>
+          <t>010-9906-3889</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>니시다 아카리</t>
+          <t>민채행</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>010-8377-8516</t>
+          <t>010-4479-2219</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>하토리 유키</t>
+          <t>타카노 마오</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>010-7239-8682</t>
+          <t>010-8903-0972</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>고노 나오</t>
+          <t>최준상</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>010-2438-2448</t>
+          <t>010-6893-1130</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>황수지</t>
+          <t>키타무라 나오</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>010-9906-3889</t>
+          <t>010-5112-5192</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>민채행</t>
+          <t>오쿠보 루이</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>010-4479-2219</t>
+          <t>010-5366-6107</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>타카노 마오</t>
+          <t>카츠타 마유토</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>010-8903-0972</t>
+          <t>010-3947-2015</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>최준상</t>
+          <t>사와다 에리</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>010-6893-1130</t>
+          <t>010-5677-0413</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>키타무라 나오</t>
+          <t>가와시마 란</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>010-5112-5192</t>
+          <t>010-3008-3176</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>오쿠보 루이</t>
+          <t>만쿠모 아스카</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>010-5366-6107</t>
+          <t>010-2579-4718</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>카츠타 마유토</t>
+          <t>권유우</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>010-3947-2015</t>
+          <t>010-6314-7752</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>사와다 에리</t>
+          <t>토쿠시마 사야카</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>010-5677-0413</t>
+          <t>010-9333-3332</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>가와시마 란</t>
+          <t>히라사와 미나기</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>010-3008-3176</t>
+          <t>010-9542-6515</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>만쿠모 아스카</t>
+          <t>박선연</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>010-2579-4718</t>
+          <t>010-9828-6875</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>권유우</t>
+          <t>사쿠라바 하루카</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>010-6314-7752</t>
+          <t>010-8059-3380</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>토쿠시마 사야카</t>
+          <t>이치야나기 유카</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>010-9333-3332</t>
+          <t>010-4854-5007</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>히라사와 미나기</t>
+          <t>무타구치 토모미</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>010-9542-6515</t>
+          <t>010-8308-0498</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>박선연</t>
+          <t>오오가네 메구미</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>010-9828-6875</t>
+          <t>010-5957-7477</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>사쿠라바 하루카</t>
+          <t>히라이 루카</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>010-8059-3380</t>
+          <t>010-8362-3074</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>이치야나기 유카</t>
+          <t>이유빈</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>010-4854-5007</t>
+          <t>010-3611-8751</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>무타구치 토모미</t>
+          <t>김혜원</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>010-8308-0498</t>
+          <t>010-6695-7188</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>오오가네 메구미</t>
+          <t>히라바야시 레이</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>010-5957-7477</t>
+          <t>010-7560-4219</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>히라이 루카</t>
+          <t>아카네</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>010-8362-3074</t>
+          <t>010-6208-4102</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>이유빈</t>
+          <t>오가와 치카</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>010-3611-8751</t>
+          <t>010-8236-8092</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>김혜원</t>
+          <t>가미키 시호</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>010-6695-7188</t>
+          <t>010-8645-3059</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>히라바야시 레이</t>
+          <t>아스카</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>010-7560-4219</t>
+          <t>010-5365-7898</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>아카네</t>
+          <t>히라이 리나</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>010-6208-4102</t>
+          <t>010-2375-4425</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>오가와 치카</t>
+          <t>무라이 세나</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>010-8236-8092</t>
+          <t>010-3836-3077</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>가미키 시호</t>
+          <t>아라마치 루나</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>010-8645-3059</t>
+          <t>010-8457-9081</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>아스카</t>
+          <t>타케이 치즈루</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>010-5365-7898</t>
+          <t>010-5715-7430</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>히라이 리나</t>
+          <t>치에미</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>010-2375-4425</t>
+          <t>010-7151-3507</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>무라이 세나</t>
+          <t>나가타 카오리</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>010-3836-3077</t>
+          <t>010-9699-8895</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>아라마치 루나</t>
+          <t>츠네 케이코</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>010-8457-9081</t>
+          <t>010-2737-1873</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>타케이 치즈루</t>
+          <t>시라이시 유미카</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>010-5715-7430</t>
+          <t>010-4003-7241</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>치에미</t>
+          <t>치쿠 우타코</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>010-7151-3507</t>
+          <t>010-7728-8221</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>나가타 카오리</t>
+          <t>메이</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>010-9699-8895</t>
+          <t>010-8098-6528</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>츠네 케이코</t>
+          <t>키타하라 마유</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>010-2737-1873</t>
+          <t>010-5659-8517</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>시라이시 유미카</t>
+          <t>다나카 시오리</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>010-4003-7241</t>
+          <t>010-2199-3351</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>치쿠 우타코</t>
+          <t>양승연</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>010-7728-8221</t>
+          <t>010-8358-2432</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>메이</t>
+          <t>무토 코요미</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>010-8098-6528</t>
+          <t>010-5803-4188</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>키타하라 마유</t>
+          <t>가츠라기 미사키</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>010-5659-8517</t>
+          <t>010-4092-7782</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>다나카 시오리</t>
+          <t>나나</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>010-2199-3351</t>
+          <t>010-7359-0032</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>양승연</t>
+          <t>키타가와 아야네</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>010-8358-2432</t>
+          <t>010-8199-5039</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>무토 코요미</t>
+          <t>하야시 사라</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>010-5803-4188</t>
+          <t>010-5885-5779</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>가츠라기 미사키</t>
+          <t>아라카와 마리리</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>010-4092-7782</t>
+          <t>010-5129-9134</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>나나</t>
+          <t>하야시 아카네</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>010-7359-0032</t>
+          <t>010-8296-4718</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>키타가와 아야네</t>
+          <t>김하은</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>010-8199-5039</t>
+          <t>010-7404-9426</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>하야시 사라</t>
+          <t>강푸른</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>010-5885-5779</t>
+          <t>010-5750-1621</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>아라카와 마리리</t>
+          <t>군지 카나</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>010-5129-9134</t>
+          <t>010-4912-2462</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>하야시 아카네</t>
+          <t>야마자키 히나노</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>010-8296-4718</t>
+          <t>010-7990-9706</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>김하은</t>
+          <t>요시다 아야노</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>010-7404-9426</t>
+          <t>010-7585-1350</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>강푸른</t>
+          <t>쿠로키 세이카</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>010-5750-1621</t>
+          <t>010-4415-5992</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>군지 카나</t>
+          <t>히라시마 하루카</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>010-4912-2462</t>
+          <t>010-3904-5438</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>야마자키 히나노</t>
+          <t>김현수</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>010-7990-9706</t>
+          <t>010-2944-6923</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>요시다 아야노</t>
+          <t>고 아이나</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>010-7585-1350</t>
+          <t>010-2557-5595</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>쿠로키 세이카</t>
+          <t>오오다니 요시미</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>010-4415-5992</t>
+          <t>010-3368-1244</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>히라시마 하루카</t>
+          <t>미야이리 치히로</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>010-3904-5438</t>
+          <t>010-2196-3025</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>김현수</t>
+          <t>히나타 미노리</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>010-2944-6923</t>
+          <t>010-5590-9781</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>고 아이나</t>
+          <t>이 히로코</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>010-2557-5595</t>
+          <t>010-7686-2367</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>오오다니 요시미</t>
+          <t>엔도 유나</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>010-3368-1244</t>
+          <t>010-7940-3269</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>미야이리 치히로</t>
+          <t>오키츠 요코</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>010-2196-3025</t>
+          <t>010-2372-5045</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>히나타 미노리</t>
+          <t>박선하</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>010-5590-9781</t>
+          <t>010-2214-4021</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>이 히로코</t>
+          <t>사토 유카</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>010-7686-2367</t>
+          <t>010-5693-4107</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>엔도 유나</t>
+          <t>와타나베 미스즈</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>010-7940-3269</t>
+          <t>010-3974-4843</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>오키츠 요코</t>
+          <t>오카모토 마코</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>010-2372-5045</t>
+          <t>010-6721-5586</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>박선하</t>
+          <t>타나카 치사</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>010-2214-4021</t>
+          <t>010-3535-0887</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>사토 유카</t>
+          <t>요시이리 사키</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>010-5693-4107</t>
+          <t>010-8334-4768</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>와타나베 미스즈</t>
+          <t>호리이케 사에</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>010-3974-4843</t>
+          <t>010-7207-6766</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>오카모토 마코</t>
+          <t>타케모토 에리</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>010-6721-5586</t>
+          <t>010-7617-6713</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>타나카 치사</t>
+          <t>사이토우 에미</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>010-3535-0887</t>
+          <t>010-2179-8986</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>요시이리 사키</t>
+          <t>우메다 히토미</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>010-8334-4768</t>
+          <t>010-8807-0216</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>호리이케 사에</t>
+          <t>이토야 유이</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>010-7207-6766</t>
+          <t>010-5723-8798</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>타케모토 에리</t>
+          <t>야스다 사쿠라코</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>010-7617-6713</t>
+          <t>010-5819-6626</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>사이토우 에미</t>
+          <t>아베 마키코</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>010-2179-8986</t>
+          <t>010-3379-1841</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>우메다 히토미</t>
+          <t>유모모</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>010-8807-0216</t>
+          <t>010-3418-7732</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>이토야 유이</t>
+          <t>사코나카 레나</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>010-5723-8798</t>
+          <t>010-4302-1150</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>야스다 사쿠라코</t>
+          <t>요시다 모모카</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>010-5819-6626</t>
+          <t>010-8836-4026</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>아베 마키코</t>
+          <t>사토 아카네</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>010-3379-1841</t>
+          <t>010-5675-1669</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>유모모</t>
+          <t>김영희</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>010-3418-7732</t>
+          <t>010-5195-0680</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>사코나카 레나</t>
+          <t>타카야마 아사리</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>010-4302-1150</t>
+          <t>010-5530-0048</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>요시다 모모카</t>
+          <t>요시미 아이리</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>010-8836-4026</t>
+          <t>010-7657-6384</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>사토 아카네</t>
+          <t>오카무라 칸나</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>010-5675-1669</t>
+          <t>010-2134-8115</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>카와하타 유리나</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>010-5195-0680</t>
+          <t>010-2238-8767</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>타카야마 아사리</t>
+          <t>아오야마 코코로</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>010-5530-0048</t>
+          <t>010-6526-9944</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>키타무라 에미</t>
+          <t>츠지 마리모</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>080-9759-3323</t>
+          <t>010-6486-6870</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>요시미 아이리</t>
+          <t>김안</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>010-7657-6384</t>
+          <t>010-9508-2663</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>오카무라 칸나</t>
+          <t>이세영</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>010-2134-8115</t>
+          <t>010-3929-5838</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>카와하타 유리나</t>
+          <t>야마자키 히토미</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>010-2238-8767</t>
+          <t>010-2946-2282</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>아오야마 코코로</t>
+          <t>노자와 사야카</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>010-6526-9944</t>
+          <t>010-2476-0474</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>츠지 마리모</t>
+          <t>시마모리 사유키</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>010-6486-6870</t>
+          <t>010-9748-9509</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>김안</t>
+          <t>나가하타 에리</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>010-9508-2663</t>
+          <t>010-8480-5784</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>이세영</t>
+          <t>스기오카 나츠</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>010-3929-5838</t>
+          <t>010-6516-5649</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>야마자키 히토미</t>
+          <t>우에리</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>010-2946-2282</t>
+          <t>010-2643-6673</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>노자와 사야카</t>
+          <t>하세가와 우노</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>010-2476-0474</t>
+          <t>010-5880-1825</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>시마모리 사유키</t>
+          <t>세이다 케이토</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>010-9748-9509</t>
+          <t>010-5786-2149</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>나가하타 에리</t>
+          <t>테라조노 안나</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>010-8480-5784</t>
+          <t>010-2188-9285</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>스기오카 나츠</t>
+          <t>미키</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>010-6516-5649</t>
+          <t>010-2412-3925</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>우에리</t>
+          <t>타이라 아야</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>010-2643-6673</t>
+          <t>010-3919-1425</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>하세가와 우노</t>
+          <t>이하 미즈키</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>010-5880-1825</t>
+          <t>010-7584-2492</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>세이다 케이토</t>
+          <t>야마다 사오리</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>010-5786-2149</t>
+          <t>010-6306-0693</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>테라조노 안나</t>
+          <t>최지혜</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>010-2188-9285</t>
+          <t>010-2298-6848</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>미키</t>
+          <t>오시로 아야네</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>010-2412-3925</t>
+          <t>010-7715-0390</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>타이라 아야</t>
+          <t>모리모토 아이리</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>010-3919-1425</t>
+          <t>010-6844-5079</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>이하 미즈키</t>
+          <t>스토 안나</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>010-7584-2492</t>
+          <t>010-3206-8905</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>야마다 사오리</t>
+          <t>니시가미 아야카</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>010-6306-0693</t>
+          <t>010-4836-2071</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>최지혜</t>
+          <t>오타 노아</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>010-2298-6848</t>
+          <t>010-2282-8724</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>오시로 아야네</t>
+          <t>키쿠치 호나미</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>010-7715-0390</t>
+          <t>010-8365-9809</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>모리모토 아이리</t>
+          <t>타카하시 나나</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>010-6844-5079</t>
+          <t>010-5901-8547</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>스토 안나</t>
+          <t>나카이 치호</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>010-3206-8905</t>
+          <t>010-4883-6204</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>쿠사카 미즈호</t>
+          <t>이즈미야 마도카</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>070-9039-7018</t>
+          <t>010-7682-1149</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>니시가미 아야카</t>
+          <t>스즈키 사라</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>010-4836-2071</t>
+          <t>010-8252-7882</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>오타 노아</t>
+          <t>하라다 주리</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>010-2282-8724</t>
+          <t>010-7486-8974</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>키쿠치 호나미</t>
+          <t>권 리아</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>010-8365-9809</t>
+          <t>010-8425-6010</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>타카하시 나나</t>
+          <t>후지무라 사야</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>010-5901-8547</t>
+          <t>010-8059-6416</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>나카이 치호</t>
+          <t>하루나</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>010-4883-6204</t>
+          <t>010-2753-3850</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>이즈미야 마도카</t>
+          <t>마에사와 코토미</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>010-7682-1149</t>
+          <t>010-2468-5892</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>스즈키 사라</t>
+          <t>사키</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>010-8252-7882</t>
+          <t>010-7687-0531</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>하라다 주리</t>
+          <t>손례진</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>010-7486-8974</t>
+          <t>010-3787-0501</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>권 리아</t>
+          <t>오오타케 치즈루</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>010-8425-6010</t>
+          <t>010-9976-7097</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>후지무라 사야</t>
+          <t>후지타 치나츠</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>010-8059-6416</t>
+          <t>010-4647-8022</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>하루나</t>
+          <t>카토 쿠우카</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>010-2753-3850</t>
+          <t>010-2366-8751</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>마에사와 코토미</t>
+          <t>아리나</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>010-2468-5892</t>
+          <t>010-9557-2987</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>사키</t>
+          <t>타카노 마야</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>010-7687-0531</t>
+          <t>010-9290-3922</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>손례진</t>
+          <t>미키렌</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>010-3787-0501</t>
+          <t>010-6827-5230</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>오오타케 치즈루</t>
+          <t>모치즈키 미사토</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>010-9976-7097</t>
+          <t>010-6592-0333</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>후지타 치나츠</t>
+          <t>오나미 코토카</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>010-4647-8022</t>
+          <t>010-7530-8456</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>카토 쿠우카</t>
+          <t>사이토 미사키</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>010-2366-8751</t>
+          <t>010-2472-8664</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>아리나</t>
+          <t>우라 니지호</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>010-9557-2987</t>
+          <t>010-7423-9928</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>타카노 마야</t>
+          <t>이케다 아마네</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>010-9290-3922</t>
+          <t>080-3015-1299</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>미키렌</t>
+          <t>이케나기 미오</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>010-6827-5230</t>
+          <t>010-7621-9062</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>모치즈키 미사토</t>
+          <t>미치카와 리나</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>010-6592-0333</t>
+          <t>010-7622-8602</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>오나미 코토카</t>
+          <t>세오 유카리</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>010-7530-8456</t>
+          <t>010-2186-4071</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>사이토 미사키</t>
+          <t>크레마츠 아스카</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>010-2472-8664</t>
+          <t>010-6832-0560</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>우라 니지호</t>
+          <t>스즈키 카논</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>010-7423-9928</t>
+          <t>010-6843-6998</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>이케나기 미오</t>
+          <t>노하라 아이꼬</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>010-7621-9062</t>
+          <t>010-6665-0631</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>미치카와 리나</t>
+          <t>장다희</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>010-7622-8602</t>
+          <t>010-8381-6234</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>세오 유카리</t>
+          <t>토바 준코</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>010-2186-4071</t>
+          <t>010-8456-5028</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>크레마츠 아스카</t>
+          <t>사오리</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>010-6832-0560</t>
+          <t>010-9938-0724</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>스즈키 카논</t>
+          <t>아사미</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>010-6843-6998</t>
+          <t>010-9571-1599</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>타케무라 시오하</t>
+          <t>이쿠미</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>010-7490-3175</t>
+          <t>010-2746-1528</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>후유카와 카스미</t>
+          <t>스미다 모모나</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>010-7360-5998</t>
+          <t>010-8423-4714</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>오사다 카나</t>
+          <t>전례자</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>010-2187-1826</t>
+          <t>010-8024-9820</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>마레</t>
+          <t>아메미야 아린</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>010-2830-5915</t>
+          <t>010-5764-1338</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>유게타 레이카</t>
+          <t>카지 메구미</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>010-6699-8867</t>
+          <t>010-5925-9678</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>오오누키 리사코</t>
+          <t>하리사키 마리에</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>010-2189-6146</t>
+          <t>010-7240-6371</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>이구치 아오이</t>
+          <t>야마다 키에</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
-        <is>
-          <t>010-8039-0914</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>시바키 아미</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>010-8053-0716</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>마스다 리카</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>010-4044-9770</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>노무라 사에</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>010-5722-2606</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>요시카와 리카</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>010-2475-5632</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>나메라 미키</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>010-3953-3976</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>곤도 쿠미</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>010-4985-0227</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>다나카 아야카</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>010-4080-0816</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>야마시타 세리</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>010-6829-1853</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>송춘나</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>010-2459-5439</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>시게모토 카오루</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>010-8832-8321</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>이유나</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>010-4285-4808</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>야마모토 카에데</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>010-2184-2406</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>정신영</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>010-5267-9954</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>시미즈 마리아</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>010-2190-6977</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>아사이미도리</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>010-7479-7379</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>사이토 아카네</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>010-9748-6355</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>야수이 레이코</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>010-6470-3314</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>츠무라 유우키</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>010-4259-7925</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>KAWANO KANA</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>010-7297-2589</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>오노 마리</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>010-5756-2674</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>카사하라 쇼코</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>010-8363-6572</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>아쿠토 마오</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>010-4345-9923</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>미야베 유끼에</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>010-2007-3348</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>홋타리코</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>010-2832-8564</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>사토우 리리</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>010-6829-3373</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>이히나</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>010-2267-4804</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>미나미 호노카</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>010-5450-0322</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>오카다 리나</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>010-5967-6921</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>시미즈 아카네</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>010-8249-5345</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>카와고에 나나미</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>010-4291-7733</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>다카타유노</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>010-7307-2721</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>사카구치 아야카</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>010-6862-0278</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>타카하시 리호</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>010-5865-4517</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>아라카와 마히로</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>010-2895-5280</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>이연순</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>010-8062-6302</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>나카지마 리사</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>010-3929-1572</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>호시노 하쯔미</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>010-9778-4323</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>정재연</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>010-5023-3663</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>아리마 키코</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>010-6842-4425</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>코이즈미 나나코</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>010-6624-9810</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>하세가와 히토미</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>010-5562-2801</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>토시네 유메</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>010-8022-1556</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>이샤가</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>010-5400-5103</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>스가와라 센리</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>010-8226-4156</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>쿠리스 안</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>010-6827-1963</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>미노 나나미</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>010-7623-4157</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>카게야마 나나</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>010-4452-3616</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>나야카</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>010-6740-2311</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>김천세</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>010-9887-2617</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>이유이</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>010-4830-7629</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>노자키 네네</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>010-9726-1156</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>야마모토 치카코</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>010-9642-7704</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>우카</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>010-7444-6546</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>우에마츠 사야까</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>010-8925-5060</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>요시카와 호노카</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>010-8306-1277</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>010-8991-7784</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>010-8991-7784</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>010-239-6219</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>010-239-6219</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>이타가키 라카</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>010-2942-7290</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>미나미 미소라</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>010-6895-8965</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>호리카와 히이나</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>010-9538-3220</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>하루나</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>010-2297-7675</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>이가라시 안</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>010-2150-0069</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>리 쿄우네</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>010-6715-5322</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>야마시타 마이</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>010-8096-5458</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>방기로</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>010-6554-4261</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>오오타케 마이</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>010-6827-9560</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>최채원</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>010-8210-8885</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>오가와 요우카</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>010-4413-0372</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>츠지무라 유미</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>010-5727-7518</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>노하라 아이꼬</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>010-6665-0631</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>장다희</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>010-8381-6234</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>토바 준코</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>010-8456-5028</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>사오리</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>010-9938-0724</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>아사미</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>010-9571-1599</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>이쿠미</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>010-2746-1528</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>스미다 모모나</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>010-8423-4714</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>전례자</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>010-8024-9820</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>아메미야 아린</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>010-5764-1338</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>카지 메구미</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>010-5925-9678</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>하리사키 마리에</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>010-7240-6371</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>야마다 키에</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
         <is>
           <t>010-4003-5231</t>
         </is>
